--- a/VerveStacks_ESP_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ESP_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4DED370-CEA7-46C1-91FF-FF409757ADB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BA7C7FE-2CC0-49FB-B911-F2E6F472C070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -906,16 +906,64 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ESP_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ESP_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ESP_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ESP_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ESP_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ESP_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ESP_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ESP_013</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_ESP_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_solelc_spv_ESP_005</t>
@@ -924,18 +972,6 @@
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ESP_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ESP_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ESP_007</t>
   </si>
   <si>
@@ -948,6 +984,24 @@
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ESP_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ESP_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ESP_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ESP_014</t>
   </si>
   <si>
@@ -972,60 +1026,6 @@
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ESP_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ESP_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ESP_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ESP_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ESP_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ESP_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ESP_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ESP_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ESP_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ESP_025</t>
   </si>
   <si>
@@ -1074,24 +1074,51 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w170424446-400_ESP,e_w170424455-400_ESP,e_w1172185252-400_ESP,e_w144767090-400_ESP,e_w170424447-400_ESP,e_w144787749-400_ESP,e_w181664117-400_ESP,e_w170961288-400_ESP</t>
+  </si>
+  <si>
+    <t>e_w144942113-400_ESP,e_w144941889-400_ESP,e_w145171008-400_ESP,e_w675714143-400_ESP,e_ES311-400_ESP,e_ES289-400_ESP,e_ES308-400_ESP,e_ES287-400_ESP</t>
+  </si>
+  <si>
+    <t>e_w77640470-400_ESP,e_w145823172-400_ESP,e_ES264-400_ESP,e_w126881765-400_ESP,e_ES212-400_ESP,e_w145302700-400_ESP</t>
+  </si>
+  <si>
+    <t>e_w51188420-400_ESP,e_w986410945-400_ESP,e_w134884956-400_ESP,e_ES266-400_ESP,e_w986410926-400_ESP,e_w144327157-400_ESP,e_w701397734-400_ESP,e_ES174-400_ESP,e_ES139-400_ESP</t>
+  </si>
+  <si>
+    <t>e_ES138-400_ESP,e_w178294745-400_ESP,e_w683892938-400_ESP,e_w340399370-400_ESP</t>
+  </si>
+  <si>
+    <t>e_w1218840771-400_ESP,e_w104370242-400_ESP,e_w143483666-400_ESP,e_w187645709-400_ESP,e_w169883205-400_ESP,e_w103158873-400_ESP,e_w626886449-400_ESP,e_w189184555-400_ESP</t>
+  </si>
+  <si>
+    <t>e_ES334-400_ESP,e_w1054312727-400_ESP,e_w651711449-400_ESP,e_w1267694217-400_ESP,e_w51188420-400_ESP,e_w1246916016-400_ESP,e_w788716327-400_ESP,e_w1246115410-400_ESP,e_w593535391-400_ESP,e_w1032009205-400_ESP,e_w181664117-400_ESP,e_w168357739-400_ESP</t>
+  </si>
+  <si>
     <t>e_w226363063-400_ESP,e_w181652542-400_ESP,e_ES207-400_ESP,e_w153232112-400_ESP,e_ES189-400_ESP,e_w931602168-400_ESP,e_ES289-400_ESP,e_w145823172-400_ESP</t>
   </si>
   <si>
+    <t>e_w88760627-400_ESP,e_w196207064-400_ESP,e_w181912569-400_ESP,e_ES39-400_ESP</t>
+  </si>
+  <si>
     <t>e_w1272548315-400_ESP,e_w1270848181-400_ESP,e_w159930931-400_ESP,e_w86512030-400_ESP</t>
   </si>
   <si>
-    <t>e_w1218840771-400_ESP,e_w104370242-400_ESP,e_w143483666-400_ESP,e_w187645709-400_ESP,e_w169883205-400_ESP,e_w103158873-400_ESP,e_w626886449-400_ESP,e_w189184555-400_ESP</t>
-  </si>
-  <si>
-    <t>e_ES334-400_ESP,e_w1054312727-400_ESP,e_w651711449-400_ESP,e_w1267694217-400_ESP,e_w51188420-400_ESP,e_w1246916016-400_ESP,e_w788716327-400_ESP,e_w1246115410-400_ESP,e_w593535391-400_ESP,e_w1032009205-400_ESP,e_w181664117-400_ESP,e_w168357739-400_ESP</t>
-  </si>
-  <si>
     <t>e_ES87-400_ESP,e_w169523046-400_ESP,e_ES178-400_ESP,e_r16809528-400_ESP,e_r10295969-400_ESP,e_w178294745-400_ESP</t>
   </si>
   <si>
     <t>e_ES130-400_ESP,e_w181912569-400_ESP,e_w143207685-400_ESP,e_ES118-400_ESP</t>
   </si>
   <si>
+    <t>e_w283348372-400_ESP,e_w144138420-400_ESP,e_w74384031-400_ESP,e_w85817084-400_ESP,e_w170479580-400_ESP,e_ES101-400_ESP</t>
+  </si>
+  <si>
+    <t>e_w222895334-400_ESP,e_ES251-400_ESP,e_w983523978-400_ESP,e_w260018670-400_ESP,e_ES233-400_ESP,e_w1120397197-400_ESP,e_w181652542-400_ESP,e_w148488880-400_ESP,e_ES258-400_ESP</t>
+  </si>
+  <si>
+    <t>e_w190236352-400_ESP,e_w86512030-400_ESP,e_w1266081844-400_ESP,e_w90829734-400_ESP</t>
+  </si>
+  <si>
     <t>e_w170946426-400_ESP,e_w145461765-400_ESP,e_w97937366-400_ESP,e_w1042227719-400_ESP,e_w222895334-400_ESP,e_ES339-400_ESP,e_w148488880-400_ESP</t>
   </si>
   <si>
@@ -1104,33 +1131,6 @@
     <t>e_w1028926498-400_ESP,e_w169999915-400_ESP,e_ES150-400_ESP,e_w169867109-400_ESP,e_w143207685-400_ESP,e_w169867119-400_ESP</t>
   </si>
   <si>
-    <t>e_w170424446-400_ESP,e_w170424455-400_ESP,e_w1172185252-400_ESP,e_w144767090-400_ESP,e_w170424447-400_ESP,e_w144787749-400_ESP,e_w181664117-400_ESP,e_w170961288-400_ESP</t>
-  </si>
-  <si>
-    <t>e_w144942113-400_ESP,e_w144941889-400_ESP,e_w145171008-400_ESP,e_w675714143-400_ESP,e_ES311-400_ESP,e_ES289-400_ESP,e_ES308-400_ESP,e_ES287-400_ESP</t>
-  </si>
-  <si>
-    <t>e_w77640470-400_ESP,e_w145823172-400_ESP,e_ES264-400_ESP,e_w126881765-400_ESP,e_ES212-400_ESP,e_w145302700-400_ESP</t>
-  </si>
-  <si>
-    <t>e_w51188420-400_ESP,e_w986410945-400_ESP,e_w134884956-400_ESP,e_ES266-400_ESP,e_w986410926-400_ESP,e_w144327157-400_ESP,e_w701397734-400_ESP,e_ES174-400_ESP,e_ES139-400_ESP</t>
-  </si>
-  <si>
-    <t>e_ES138-400_ESP,e_w178294745-400_ESP,e_w683892938-400_ESP,e_w340399370-400_ESP</t>
-  </si>
-  <si>
-    <t>e_w283348372-400_ESP,e_w144138420-400_ESP,e_w74384031-400_ESP,e_w85817084-400_ESP,e_w170479580-400_ESP,e_ES101-400_ESP</t>
-  </si>
-  <si>
-    <t>e_w222895334-400_ESP,e_ES251-400_ESP,e_w983523978-400_ESP,e_w260018670-400_ESP,e_ES233-400_ESP,e_w1120397197-400_ESP,e_w181652542-400_ESP,e_w148488880-400_ESP,e_ES258-400_ESP</t>
-  </si>
-  <si>
-    <t>e_w190236352-400_ESP,e_w86512030-400_ESP,e_w1266081844-400_ESP,e_w90829734-400_ESP</t>
-  </si>
-  <si>
-    <t>e_w88760627-400_ESP,e_w196207064-400_ESP,e_w181912569-400_ESP,e_ES39-400_ESP</t>
-  </si>
-  <si>
     <t>e_w103158873-400_ESP,e_w73511619-400_ESP,e_w103511952-400_ESP,e_w701397734-400_ESP,e_w52516392-400_ESP,e_w81152317-400_ESP,e_w189577215-400_ESP,e_ES120-400_ESP,e_w118057369-400_ESP</t>
   </si>
   <si>
@@ -1152,6 +1152,24 @@
     <t>e_w931181199-400_ESP,e_ES136-400_ESP,e_w129767234-400_ESP,e_ES118-400_ESP,e_ES178-400_ESP</t>
   </si>
   <si>
+    <t>distr_wonelc_won_ESP_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_ESP_011</t>
   </si>
   <si>
@@ -1164,144 +1182,144 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_wonelc_won_ESP_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ESP_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_ESP_009</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ESP_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ESP_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_ESP_015</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
+    <t>elc_won_ESP_022</t>
+  </si>
+  <si>
+    <t>e_w170479580-400_ESP,e_w170272140-400_ESP,e_w190236352-400_ESP,e_ES258-400_ESP,e_w181652542-400_ESP,e_ES207-400_ESP,e_ES189-400_ESP,e_w931602168-400_ESP,e_w1028926498-400_ESP,e_w169999915-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_025</t>
+  </si>
+  <si>
+    <t>e_ES138-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_002</t>
+  </si>
+  <si>
+    <t>e_w51188420-400_ESP,e_w986410945-400_ESP,e_ES266-400_ESP,e_w168358225-400_ESP</t>
+  </si>
+  <si>
     <t>elc_won_ESP_011</t>
   </si>
   <si>
@@ -1314,217 +1332,217 @@
     <t>e_w144487932-400_ESP,e_w97286424-400_ESP,e_ES376-400_ESP,e_ES371-400_ESP,e_w170946426-400_ESP,e_w97937366-400_ESP,e_w327268322-400_ESP,e_ES372-400_ESP</t>
   </si>
   <si>
+    <t>elc_won_ESP_008</t>
+  </si>
+  <si>
+    <t>e_w168358225-400_ESP,e_w1168861008-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_006</t>
+  </si>
+  <si>
+    <t>e_w181664117-400_ESP,e_w170954487-400_ESP,e_w145461765-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_013</t>
+  </si>
+  <si>
+    <t>e_w1218840771-400_ESP,e_w104370242-400_ESP,e_w143483666-400_ESP,e_w187645709-400_ESP,e_w169883205-400_ESP,e_w103158873-400_ESP,e_w626886449-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_003</t>
+  </si>
+  <si>
+    <t>e_w1168861008-400_ESP,e_w283348372-400_ESP,e_w27668869-400_ESP,e_w983523978-400_ESP,e_w101953901-400_ESP,e_ES233-400_ESP,e_w170272140-400_ESP,e_w226363063-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_005</t>
+  </si>
+  <si>
+    <t>e_w170424446-400_ESP,e_w170424455-400_ESP,e_w1172185252-400_ESP,e_w144487932-400_ESP,e_w170424447-400_ESP,e_w1246916016-400_ESP,e_w144787749-400_ESP,e_w181664117-400_ESP,e_w170961288-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_014</t>
+  </si>
+  <si>
+    <t>e_w134884956-400_ESP,e_w986410926-400_ESP,e_w144327157-400_ESP,e_w701397734-400_ESP,e_ES174-400_ESP,e_ES139-400_ESP,e_ES120-400_ESP,e_w283348372-400_ESP,e_w144138420-400_ESP,e_w74384031-400_ESP,e_w85817084-400_ESP,e_w118057369-400_ESP,e_w170479580-400_ESP,e_ES101-400_ESP,e_w47842260-400_ESP,e_w1272548315-400_ESP,e_w1270848181-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_007</t>
+  </si>
+  <si>
+    <t>e_w487381592-400_ESP,e_w170946426-400_ESP,e_w145461765-400_ESP,e_w222895334-400_ESP,e_w1042227719-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_001</t>
+  </si>
+  <si>
+    <t>e_ES251-400_ESP,e_w222895334-400_ESP,e_w260018670-400_ESP,e_w1120397197-400_ESP,e_w181652542-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_019</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_010</t>
+  </si>
+  <si>
+    <t>e_w593535391-400_ESP,e_w1032009205-400_ESP,e_w168357739-400_ESP,e_w576439241-400_ESP,e_ES251-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_016</t>
+  </si>
+  <si>
+    <t>e_w148488880-400_ESP,e_w1120397197-400_ESP,e_w144941889-400_ESP,e_w145171008-400_ESP,e_ES311-400_ESP,e_ES289-400_ESP,e_ES308-400_ESP,e_ES287-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_023</t>
+  </si>
+  <si>
+    <t>e_w86512030-400_ESP,e_w88760627-400_ESP,e_w1266081844-400_ESP,e_w90829734-400_ESP,e_w181912569-400_ESP,e_ES150-400_ESP,e_ES130-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_012</t>
+  </si>
+  <si>
+    <t>e_w51822825-400_ESP,e_w1141933143-400_ESP,e_w159930931-400_ESP,e_w202891403-400_ESP,e_w86512030-400_ESP,e_w115680075-400_ESP,e_w1240967180-400_ESP,e_w196207064-400_ESP,e_ES39-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_021</t>
+  </si>
+  <si>
+    <t>e_w153232112-400_ESP,e_ES289-400_ESP,e_w145823172-400_ESP,e_w77640470-400_ESP,e_ES264-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_020</t>
+  </si>
+  <si>
+    <t>e_w169867109-400_ESP,e_w143207685-400_ESP,e_w126881765-400_ESP,e_ES212-400_ESP,e_w169867119-400_ESP,e_w145302700-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_018</t>
+  </si>
+  <si>
+    <t>e_w169523046-400_ESP,e_ES178-400_ESP,e_r16809528-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_017</t>
+  </si>
+  <si>
+    <t>e_w144909709-400_ESP,e_ES339-400_ESP,e_w144942113-400_ESP,e_w129441519-400_ESP,e_ES336-400_ESP,e_w675714143-400_ESP,e_w171251565-400_ESP,e_w171256169-400_ESP,e_ES324-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_024</t>
+  </si>
+  <si>
+    <t>e_w683892938-400_ESP,e_w340399370-400_ESP</t>
+  </si>
+  <si>
     <t>elc_won_ESP_009</t>
   </si>
   <si>
     <t>e_ES334-400_ESP,e_w1054312727-400_ESP,e_w144767090-400_ESP,e_w651711449-400_ESP,e_w1267694217-400_ESP,e_w51188420-400_ESP,e_w788716327-400_ESP,e_w1246115410-400_ESP,e_w593535391-400_ESP</t>
   </si>
   <si>
-    <t>elc_won_ESP_008</t>
-  </si>
-  <si>
-    <t>e_w168358225-400_ESP,e_w1168861008-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_006</t>
-  </si>
-  <si>
-    <t>e_w181664117-400_ESP,e_w170954487-400_ESP,e_w145461765-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_005</t>
-  </si>
-  <si>
-    <t>e_w170424446-400_ESP,e_w170424455-400_ESP,e_w1172185252-400_ESP,e_w144487932-400_ESP,e_w170424447-400_ESP,e_w1246916016-400_ESP,e_w144787749-400_ESP,e_w181664117-400_ESP,e_w170961288-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_014</t>
-  </si>
-  <si>
-    <t>e_w134884956-400_ESP,e_w986410926-400_ESP,e_w144327157-400_ESP,e_w701397734-400_ESP,e_ES174-400_ESP,e_ES139-400_ESP,e_ES120-400_ESP,e_w283348372-400_ESP,e_w144138420-400_ESP,e_w74384031-400_ESP,e_w85817084-400_ESP,e_w118057369-400_ESP,e_w170479580-400_ESP,e_ES101-400_ESP,e_w47842260-400_ESP,e_w1272548315-400_ESP,e_w1270848181-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_007</t>
-  </si>
-  <si>
-    <t>e_w487381592-400_ESP,e_w170946426-400_ESP,e_w145461765-400_ESP,e_w222895334-400_ESP,e_w1042227719-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_001</t>
-  </si>
-  <si>
-    <t>e_ES251-400_ESP,e_w222895334-400_ESP,e_w260018670-400_ESP,e_w1120397197-400_ESP,e_w181652542-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_019</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_010</t>
-  </si>
-  <si>
-    <t>e_w593535391-400_ESP,e_w1032009205-400_ESP,e_w168357739-400_ESP,e_w576439241-400_ESP,e_ES251-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_016</t>
-  </si>
-  <si>
-    <t>e_w148488880-400_ESP,e_w1120397197-400_ESP,e_w144941889-400_ESP,e_w145171008-400_ESP,e_ES311-400_ESP,e_ES289-400_ESP,e_ES308-400_ESP,e_ES287-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_023</t>
-  </si>
-  <si>
-    <t>e_w86512030-400_ESP,e_w88760627-400_ESP,e_w1266081844-400_ESP,e_w90829734-400_ESP,e_w181912569-400_ESP,e_ES150-400_ESP,e_ES130-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_017</t>
-  </si>
-  <si>
-    <t>e_w144909709-400_ESP,e_ES339-400_ESP,e_w144942113-400_ESP,e_w129441519-400_ESP,e_ES336-400_ESP,e_w675714143-400_ESP,e_w171251565-400_ESP,e_w171256169-400_ESP,e_ES324-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_024</t>
-  </si>
-  <si>
-    <t>e_w683892938-400_ESP,e_w340399370-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_018</t>
-  </si>
-  <si>
-    <t>e_w169523046-400_ESP,e_ES178-400_ESP,e_r16809528-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_002</t>
-  </si>
-  <si>
-    <t>e_w51188420-400_ESP,e_w986410945-400_ESP,e_ES266-400_ESP,e_w168358225-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_022</t>
-  </si>
-  <si>
-    <t>e_w170479580-400_ESP,e_w170272140-400_ESP,e_w190236352-400_ESP,e_ES258-400_ESP,e_w181652542-400_ESP,e_ES207-400_ESP,e_ES189-400_ESP,e_w931602168-400_ESP,e_w1028926498-400_ESP,e_w169999915-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_025</t>
-  </si>
-  <si>
-    <t>e_ES138-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_012</t>
-  </si>
-  <si>
-    <t>e_w51822825-400_ESP,e_w1141933143-400_ESP,e_w159930931-400_ESP,e_w202891403-400_ESP,e_w86512030-400_ESP,e_w115680075-400_ESP,e_w1240967180-400_ESP,e_w196207064-400_ESP,e_ES39-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_021</t>
-  </si>
-  <si>
-    <t>e_w153232112-400_ESP,e_ES289-400_ESP,e_w145823172-400_ESP,e_w77640470-400_ESP,e_ES264-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_020</t>
-  </si>
-  <si>
-    <t>e_w169867109-400_ESP,e_w143207685-400_ESP,e_w126881765-400_ESP,e_ES212-400_ESP,e_w169867119-400_ESP,e_w145302700-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_013</t>
-  </si>
-  <si>
-    <t>e_w1218840771-400_ESP,e_w104370242-400_ESP,e_w143483666-400_ESP,e_w187645709-400_ESP,e_w169883205-400_ESP,e_w103158873-400_ESP,e_w626886449-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_won_ESP_003</t>
-  </si>
-  <si>
-    <t>e_w1168861008-400_ESP,e_w283348372-400_ESP,e_w27668869-400_ESP,e_w983523978-400_ESP,e_w101953901-400_ESP,e_ES233-400_ESP,e_w170272140-400_ESP,e_w226363063-400_ESP</t>
-  </si>
-  <si>
     <t>elc_won_ESP_015</t>
   </si>
   <si>
     <t>e_w1042227719-400_ESP,e_w327268322-400_ESP,e_w772400244-400_ESP,e_ES339-400_ESP</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_ESP_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_ESP_011</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ESP_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_ESP_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ESP_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
+    <t>distr_wofelc_wof_ESP_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ESP_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wofelc_wof_ESP_013</t>
@@ -1539,22 +1557,76 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ESP_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ESP_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
+    <t>elc_wof_ESP_005</t>
+  </si>
+  <si>
+    <t>e_ES210-400_ESP,e_ES208-400_ESP,e_w200253359-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_008</t>
+  </si>
+  <si>
+    <t>e_w165580300-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_018</t>
+  </si>
+  <si>
+    <t>e_w104370242-400_ESP,e_w187645709-400_ESP,e_ES1-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_012</t>
+  </si>
+  <si>
+    <t>e_ES359-400_ESP,e_w170424455-400_ESP,e_ES396-400_ESP,e_w144487932-400_ESP,e_ES395-400_ESP,e_w691036111-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_017</t>
+  </si>
+  <si>
+    <t>e_ES1-400_ESP,e_w189184555-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_003</t>
+  </si>
+  <si>
+    <t>e_w156435509-400_ESP,e_ES308-400_ESP,e_ES265-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_015</t>
+  </si>
+  <si>
+    <t>e_w683892938-400_ESP,e_w340399370-400_ESP,e_ES74-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_001</t>
+  </si>
+  <si>
+    <t>e_w144909722-400_ESP,e_w144915428-400_ESP,e_w144915438-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_002</t>
+  </si>
+  <si>
+    <t>e_w729485840-400_ESP,e_w171256169-400_ESP,e_ES324-400_ESP,e_w156435509-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_009</t>
+  </si>
+  <si>
+    <t>e_ES396-400_ESP,e_w1262722032-400_ESP,e_w170968145-400_ESP,e_w170946426-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_014</t>
+  </si>
+  <si>
+    <t>e_w1141933143-400_ESP,e_ES27-400_ESP,e_w223207745-400_ESP,e_ES5-400_ESP,e_ES37-400_ESP,e_ES40-400_ESP,e_w196207063-400_ESP,e_ES6-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_004</t>
+  </si>
+  <si>
+    <t>e_ES265-400_ESP,e_w200253359-400_ESP,e_w165580300-400_ESP</t>
   </si>
   <si>
     <t>elc_wof_ESP_011</t>
@@ -1563,76 +1635,22 @@
     <t>e_w170424455-400_ESP</t>
   </si>
   <si>
-    <t>elc_wof_ESP_009</t>
-  </si>
-  <si>
-    <t>e_ES396-400_ESP,e_w1262722032-400_ESP,e_w170968145-400_ESP,e_w170946426-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_014</t>
-  </si>
-  <si>
-    <t>e_w1141933143-400_ESP,e_ES27-400_ESP,e_w223207745-400_ESP,e_ES5-400_ESP,e_ES37-400_ESP,e_ES40-400_ESP,e_w196207063-400_ESP,e_ES6-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_004</t>
-  </si>
-  <si>
-    <t>e_ES265-400_ESP,e_w200253359-400_ESP,e_w165580300-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_005</t>
-  </si>
-  <si>
-    <t>e_ES210-400_ESP,e_ES208-400_ESP,e_w200253359-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_008</t>
-  </si>
-  <si>
-    <t>e_w165580300-400_ESP</t>
-  </si>
-  <si>
     <t>elc_wof_ESP_007</t>
   </si>
   <si>
     <t>e_w165580300-400_ESP,e_w683892938-400_ESP</t>
   </si>
   <si>
-    <t>elc_wof_ESP_015</t>
-  </si>
-  <si>
-    <t>e_w683892938-400_ESP,e_w340399370-400_ESP,e_ES74-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_018</t>
-  </si>
-  <si>
-    <t>e_w104370242-400_ESP,e_w187645709-400_ESP,e_ES1-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_012</t>
-  </si>
-  <si>
-    <t>e_ES359-400_ESP,e_w170424455-400_ESP,e_ES396-400_ESP,e_w144487932-400_ESP,e_ES395-400_ESP,e_w691036111-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_017</t>
-  </si>
-  <si>
-    <t>e_ES1-400_ESP,e_w189184555-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_003</t>
-  </si>
-  <si>
-    <t>e_w156435509-400_ESP,e_ES308-400_ESP,e_ES265-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_001</t>
-  </si>
-  <si>
-    <t>e_w144909722-400_ESP,e_w144915428-400_ESP,e_w144915438-400_ESP</t>
+    <t>elc_wof_ESP_016</t>
+  </si>
+  <si>
+    <t>e_w1218840771-400_ESP,e_ES141-400_ESP</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_010</t>
+  </si>
+  <si>
+    <t>e_w170968145-400_ESP,e_w170946426-400_ESP,e_w97937366-400_ESP,e_w327268322-400_ESP,e_w144909722-400_ESP,e_ES373-400_ESP,e_ES372-400_ESP</t>
   </si>
   <si>
     <t>elc_wof_ESP_013</t>
@@ -1645,24 +1663,6 @@
   </si>
   <si>
     <t>e_w165580300-400_ESP,e_w169729505-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_002</t>
-  </si>
-  <si>
-    <t>e_w729485840-400_ESP,e_w171256169-400_ESP,e_ES324-400_ESP,e_w156435509-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_016</t>
-  </si>
-  <si>
-    <t>e_w1218840771-400_ESP,e_ES141-400_ESP</t>
-  </si>
-  <si>
-    <t>elc_wof_ESP_010</t>
-  </si>
-  <si>
-    <t>e_w170968145-400_ESP,e_w170946426-400_ESP,e_w97937366-400_ESP,e_w327268322-400_ESP,e_w144909722-400_ESP,e_ES373-400_ESP,e_ES372-400_ESP</t>
   </si>
   <si>
     <t>e_won_ESP_001</t>
@@ -6727,7 +6727,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA660BA-CAE7-4532-991B-E0FF383E9AFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7351E95-F56B-4C13-A3A6-BEB37CC396EC}">
   <dimension ref="B9:BD36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6965,16 +6965,16 @@
         <v>259</v>
       </c>
       <c r="Y11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Z11" t="s">
         <v>315</v>
       </c>
       <c r="AA11">
-        <v>0.99760024274030834</v>
+        <v>0.99803615755387043</v>
       </c>
       <c r="AB11">
-        <v>43.995549761013756</v>
+        <v>36.003778179042861</v>
       </c>
       <c r="AD11" t="s">
         <v>258</v>
@@ -7007,10 +7007,10 @@
         <v>392</v>
       </c>
       <c r="AO11">
-        <v>0.99899835021473482</v>
+        <v>0.99766227319444256</v>
       </c>
       <c r="AP11">
-        <v>18.363579396529101</v>
+        <v>42.858324768553842</v>
       </c>
       <c r="AR11" t="s">
         <v>258</v>
@@ -7043,10 +7043,10 @@
         <v>477</v>
       </c>
       <c r="BC11">
-        <v>0.99772463345786588</v>
+        <v>0.99622841226045356</v>
       </c>
       <c r="BD11">
-        <v>41.715053272459365</v>
+        <v>69.14577522501915</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7111,16 +7111,16 @@
         <v>263</v>
       </c>
       <c r="Y12" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="Z12" t="s">
         <v>316</v>
       </c>
       <c r="AA12">
-        <v>0.99810905655110083</v>
+        <v>0.99914465285998433</v>
       </c>
       <c r="AB12">
-        <v>34.667296563150792</v>
+        <v>15.681364233621375</v>
       </c>
       <c r="AD12" t="s">
         <v>258</v>
@@ -7153,10 +7153,10 @@
         <v>394</v>
       </c>
       <c r="AO12">
-        <v>0.99851205730014336</v>
+        <v>0.99916669398891145</v>
       </c>
       <c r="AP12">
-        <v>27.278949497372452</v>
+        <v>15.27727686995606</v>
       </c>
       <c r="AR12" t="s">
         <v>258</v>
@@ -7189,10 +7189,10 @@
         <v>479</v>
       </c>
       <c r="BC12">
-        <v>0.99593310451560124</v>
+        <v>0.98696325312896338</v>
       </c>
       <c r="BD12">
-        <v>74.559750547309747</v>
+        <v>239.00702596900499</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7257,16 +7257,16 @@
         <v>265</v>
       </c>
       <c r="Y13" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="Z13" t="s">
         <v>317</v>
       </c>
       <c r="AA13">
-        <v>0.99820678006058794</v>
+        <v>0.99814882213345824</v>
       </c>
       <c r="AB13">
-        <v>32.875698889220587</v>
+        <v>33.938260886599231</v>
       </c>
       <c r="AD13" t="s">
         <v>258</v>
@@ -7299,10 +7299,10 @@
         <v>396</v>
       </c>
       <c r="AO13">
-        <v>0.99787586239643478</v>
+        <v>0.99819477422379621</v>
       </c>
       <c r="AP13">
-        <v>38.942522732029175</v>
+        <v>33.095805897069312</v>
       </c>
       <c r="AR13" t="s">
         <v>258</v>
@@ -7335,10 +7335,10 @@
         <v>481</v>
       </c>
       <c r="BC13">
-        <v>0.99606887563782476</v>
+        <v>0.99437962134878188</v>
       </c>
       <c r="BD13">
-        <v>72.070613306545894</v>
+        <v>103.04027527233119</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7403,16 +7403,16 @@
         <v>267</v>
       </c>
       <c r="Y14" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Z14" t="s">
         <v>318</v>
       </c>
       <c r="AA14">
-        <v>0.99775375490950224</v>
+        <v>0.99786785981541182</v>
       </c>
       <c r="AB14">
-        <v>41.181159992459165</v>
+        <v>39.089236717450547</v>
       </c>
       <c r="AD14" t="s">
         <v>258</v>
@@ -7445,10 +7445,10 @@
         <v>398</v>
       </c>
       <c r="AO14">
-        <v>0.99683158225161861</v>
+        <v>0.99899835021473482</v>
       </c>
       <c r="AP14">
-        <v>58.087658720326083</v>
+        <v>18.363579396529101</v>
       </c>
       <c r="AR14" t="s">
         <v>258</v>
@@ -7481,10 +7481,10 @@
         <v>483</v>
       </c>
       <c r="BC14">
-        <v>0.98551300226432692</v>
+        <v>0.99441440005832071</v>
       </c>
       <c r="BD14">
-        <v>265.59495848733906</v>
+        <v>102.40266559745355</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7549,16 +7549,16 @@
         <v>269</v>
       </c>
       <c r="Y15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Z15" t="s">
         <v>319</v>
       </c>
       <c r="AA15">
-        <v>0.99820226605144713</v>
+        <v>0.99900389196026074</v>
       </c>
       <c r="AB15">
-        <v>32.95845572346942</v>
+        <v>18.261980728552661</v>
       </c>
       <c r="AD15" t="s">
         <v>258</v>
@@ -7591,10 +7591,10 @@
         <v>400</v>
       </c>
       <c r="AO15">
-        <v>0.99737738958465394</v>
+        <v>0.99851205730014336</v>
       </c>
       <c r="AP15">
-        <v>48.081190948010828</v>
+        <v>27.278949497372452</v>
       </c>
       <c r="AR15" t="s">
         <v>258</v>
@@ -7627,10 +7627,10 @@
         <v>485</v>
       </c>
       <c r="BC15">
-        <v>0.99622841226045356</v>
+        <v>0.99700047427460914</v>
       </c>
       <c r="BD15">
-        <v>69.14577522501915</v>
+        <v>54.991304965499957</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7695,16 +7695,16 @@
         <v>271</v>
       </c>
       <c r="Y16" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="Z16" t="s">
         <v>320</v>
       </c>
       <c r="AA16">
-        <v>0.99754016554385327</v>
+        <v>0.99820678006058794</v>
       </c>
       <c r="AB16">
-        <v>45.096965029355985</v>
+        <v>32.875698889220587</v>
       </c>
       <c r="AD16" t="s">
         <v>258</v>
@@ -7737,10 +7737,10 @@
         <v>402</v>
       </c>
       <c r="AO16">
-        <v>0.99822941429085754</v>
+        <v>0.99683158225161861</v>
       </c>
       <c r="AP16">
-        <v>32.46073800094517</v>
+        <v>58.087658720326083</v>
       </c>
       <c r="AR16" t="s">
         <v>258</v>
@@ -7773,10 +7773,10 @@
         <v>487</v>
       </c>
       <c r="BC16">
-        <v>0.98696325312896338</v>
+        <v>0.99296404312964126</v>
       </c>
       <c r="BD16">
-        <v>239.00702596900499</v>
+        <v>128.99254262324413</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7841,16 +7841,16 @@
         <v>273</v>
       </c>
       <c r="Y17" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Z17" t="s">
         <v>321</v>
       </c>
       <c r="AA17">
-        <v>0.99652495247103934</v>
+        <v>0.99775375490950224</v>
       </c>
       <c r="AB17">
-        <v>63.709204697612876</v>
+        <v>41.181159992459165</v>
       </c>
       <c r="AD17" t="s">
         <v>258</v>
@@ -7883,10 +7883,10 @@
         <v>404</v>
       </c>
       <c r="AO17">
-        <v>0.99858692093222978</v>
+        <v>0.99737738958465394</v>
       </c>
       <c r="AP17">
-        <v>25.90644957578818</v>
+        <v>48.081190948010828</v>
       </c>
       <c r="AR17" t="s">
         <v>258</v>
@@ -7919,10 +7919,10 @@
         <v>489</v>
       </c>
       <c r="BC17">
-        <v>0.98319813611365281</v>
+        <v>0.99372948663399951</v>
       </c>
       <c r="BD17">
-        <v>308.03417124969855</v>
+        <v>114.95941171000901</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7987,16 +7987,16 @@
         <v>275</v>
       </c>
       <c r="Y18" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="Z18" t="s">
         <v>322</v>
       </c>
       <c r="AA18">
-        <v>0.99694914525426248</v>
+        <v>0.99760024274030834</v>
       </c>
       <c r="AB18">
-        <v>55.93233700518811</v>
+        <v>43.995549761013756</v>
       </c>
       <c r="AD18" t="s">
         <v>258</v>
@@ -8029,10 +8029,10 @@
         <v>406</v>
       </c>
       <c r="AO18">
-        <v>0.99691296533138052</v>
+        <v>0.99738967567885828</v>
       </c>
       <c r="AP18">
-        <v>56.595635591356405</v>
+        <v>47.855945887599148</v>
       </c>
       <c r="AR18" t="s">
         <v>258</v>
@@ -8065,10 +8065,10 @@
         <v>491</v>
       </c>
       <c r="BC18">
-        <v>0.99372948663399951</v>
+        <v>0.99729737295219256</v>
       </c>
       <c r="BD18">
-        <v>114.95941171000901</v>
+        <v>49.548162543136158</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8133,16 +8133,16 @@
         <v>277</v>
       </c>
       <c r="Y19" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="Z19" t="s">
         <v>323</v>
       </c>
       <c r="AA19">
-        <v>0.99783229073864799</v>
+        <v>0.99844308301553419</v>
       </c>
       <c r="AB19">
-        <v>39.741336458120216</v>
+        <v>28.543478048539875</v>
       </c>
       <c r="AD19" t="s">
         <v>258</v>
@@ -8175,10 +8175,10 @@
         <v>408</v>
       </c>
       <c r="AO19">
-        <v>0.99767669102808521</v>
+        <v>0.99928399407691448</v>
       </c>
       <c r="AP19">
-        <v>42.593997818438375</v>
+        <v>13.126775256568077</v>
       </c>
       <c r="AR19" t="s">
         <v>258</v>
@@ -8211,10 +8211,10 @@
         <v>493</v>
       </c>
       <c r="BC19">
-        <v>0.99437962134878188</v>
+        <v>0.99205612047457914</v>
       </c>
       <c r="BD19">
-        <v>103.04027527233119</v>
+        <v>145.63779129938152</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8279,16 +8279,16 @@
         <v>279</v>
       </c>
       <c r="Y20" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z20" t="s">
         <v>324</v>
       </c>
       <c r="AA20">
-        <v>0.99854419231621216</v>
+        <v>0.99810905655110083</v>
       </c>
       <c r="AB20">
-        <v>26.689807536110646</v>
+        <v>34.667296563150792</v>
       </c>
       <c r="AD20" t="s">
         <v>258</v>
@@ -8318,13 +8318,13 @@
         <v>409</v>
       </c>
       <c r="AN20" t="s">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="AO20">
-        <v>0.99768994666600497</v>
+        <v>0.99822941429085754</v>
       </c>
       <c r="AP20">
-        <v>42.350977789908335</v>
+        <v>32.46073800094517</v>
       </c>
       <c r="AR20" t="s">
         <v>258</v>
@@ -8357,10 +8357,10 @@
         <v>495</v>
       </c>
       <c r="BC20">
-        <v>0.99441440005832071</v>
+        <v>0.99593310451560124</v>
       </c>
       <c r="BD20">
-        <v>102.40266559745355</v>
+        <v>74.559750547309747</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8425,16 +8425,16 @@
         <v>281</v>
       </c>
       <c r="Y21" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="Z21" t="s">
         <v>325</v>
       </c>
       <c r="AA21">
-        <v>0.99803615755387043</v>
+        <v>0.99820226605144713</v>
       </c>
       <c r="AB21">
-        <v>36.003778179042861</v>
+        <v>32.95845572346942</v>
       </c>
       <c r="AD21" t="s">
         <v>258</v>
@@ -8461,16 +8461,16 @@
         <v>361</v>
       </c>
       <c r="AM21" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN21" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO21">
-        <v>0.99764926878204374</v>
+        <v>0.99858692093222978</v>
       </c>
       <c r="AP21">
-        <v>43.096738995865174</v>
+        <v>25.90644957578818</v>
       </c>
       <c r="AR21" t="s">
         <v>258</v>
@@ -8503,10 +8503,10 @@
         <v>497</v>
       </c>
       <c r="BC21">
-        <v>0.99700047427460914</v>
+        <v>0.99606887563782476</v>
       </c>
       <c r="BD21">
-        <v>54.991304965499957</v>
+        <v>72.070613306545894</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8571,16 +8571,16 @@
         <v>283</v>
       </c>
       <c r="Y22" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Z22" t="s">
         <v>326</v>
       </c>
       <c r="AA22">
-        <v>0.99914465285998433</v>
+        <v>0.99754016554385327</v>
       </c>
       <c r="AB22">
-        <v>15.681364233621375</v>
+        <v>45.096965029355985</v>
       </c>
       <c r="AD22" t="s">
         <v>258</v>
@@ -8607,16 +8607,16 @@
         <v>363</v>
       </c>
       <c r="AM22" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN22" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO22">
-        <v>0.99917672012857084</v>
+        <v>0.99691296533138052</v>
       </c>
       <c r="AP22">
-        <v>15.093464309533656</v>
+        <v>56.595635591356405</v>
       </c>
       <c r="AR22" t="s">
         <v>258</v>
@@ -8649,10 +8649,10 @@
         <v>499</v>
       </c>
       <c r="BC22">
-        <v>0.99296404312964126</v>
+        <v>0.98551300226432692</v>
       </c>
       <c r="BD22">
-        <v>128.99254262324413</v>
+        <v>265.59495848733906</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8717,16 +8717,16 @@
         <v>285</v>
       </c>
       <c r="Y23" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="Z23" t="s">
         <v>327</v>
       </c>
       <c r="AA23">
-        <v>0.99814882213345824</v>
+        <v>0.99835863162018557</v>
       </c>
       <c r="AB23">
-        <v>33.938260886599231</v>
+        <v>30.091753629930697</v>
       </c>
       <c r="AD23" t="s">
         <v>258</v>
@@ -8753,16 +8753,16 @@
         <v>365</v>
       </c>
       <c r="AM23" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN23" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO23">
-        <v>0.99870468347604002</v>
+        <v>0.99767669102808521</v>
       </c>
       <c r="AP23">
-        <v>23.747469605933066</v>
+        <v>42.593997818438375</v>
       </c>
       <c r="AR23" t="s">
         <v>258</v>
@@ -8795,10 +8795,10 @@
         <v>501</v>
       </c>
       <c r="BC23">
-        <v>0.99729737295219256</v>
+        <v>0.99772463345786588</v>
       </c>
       <c r="BD23">
-        <v>49.548162543136158</v>
+        <v>41.715053272459365</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8863,16 +8863,16 @@
         <v>287</v>
       </c>
       <c r="Y24" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="Z24" t="s">
         <v>328</v>
       </c>
       <c r="AA24">
-        <v>0.99786785981541182</v>
+        <v>0.99785055087302266</v>
       </c>
       <c r="AB24">
-        <v>39.089236717450547</v>
+        <v>39.406567327917379</v>
       </c>
       <c r="AD24" t="s">
         <v>258</v>
@@ -8899,16 +8899,16 @@
         <v>367</v>
       </c>
       <c r="AM24" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN24" t="s">
-        <v>417</v>
+        <v>340</v>
       </c>
       <c r="AO24">
-        <v>0.99811627933819014</v>
+        <v>0.99768994666600497</v>
       </c>
       <c r="AP24">
-        <v>34.534878799847206</v>
+        <v>42.350977789908335</v>
       </c>
       <c r="AR24" t="s">
         <v>258</v>
@@ -8941,10 +8941,10 @@
         <v>503</v>
       </c>
       <c r="BC24">
-        <v>0.99631611357458616</v>
+        <v>0.98319813611365281</v>
       </c>
       <c r="BD24">
-        <v>67.537917799253435</v>
+        <v>308.03417124969855</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9009,16 +9009,16 @@
         <v>289</v>
       </c>
       <c r="Y25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Z25" t="s">
         <v>329</v>
       </c>
       <c r="AA25">
-        <v>0.99900389196026074</v>
+        <v>0.99844993371564827</v>
       </c>
       <c r="AB25">
-        <v>18.261980728552661</v>
+        <v>28.417881879781795</v>
       </c>
       <c r="AD25" t="s">
         <v>258</v>
@@ -9051,10 +9051,10 @@
         <v>419</v>
       </c>
       <c r="AO25">
-        <v>0.99868644475480806</v>
+        <v>0.99764926878204374</v>
       </c>
       <c r="AP25">
-        <v>24.081846161853086</v>
+        <v>43.096738995865174</v>
       </c>
       <c r="AR25" t="s">
         <v>258</v>
@@ -9087,10 +9087,10 @@
         <v>505</v>
       </c>
       <c r="BC25">
-        <v>0.99647965026436902</v>
+        <v>0.99331560634963856</v>
       </c>
       <c r="BD25">
-        <v>64.539745153233895</v>
+        <v>122.54721692329359</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9155,16 +9155,16 @@
         <v>291</v>
       </c>
       <c r="Y26" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="Z26" t="s">
         <v>330</v>
       </c>
       <c r="AA26">
-        <v>0.99835863162018557</v>
+        <v>0.99652495247103934</v>
       </c>
       <c r="AB26">
-        <v>30.091753629930697</v>
+        <v>63.709204697612876</v>
       </c>
       <c r="AD26" t="s">
         <v>258</v>
@@ -9197,10 +9197,10 @@
         <v>421</v>
       </c>
       <c r="AO26">
-        <v>0.99949680967458154</v>
+        <v>0.99917672012857084</v>
       </c>
       <c r="AP26">
-        <v>9.2251559660040208</v>
+        <v>15.093464309533656</v>
       </c>
       <c r="AR26" t="s">
         <v>258</v>
@@ -9233,10 +9233,10 @@
         <v>507</v>
       </c>
       <c r="BC26">
-        <v>0.99205612047457914</v>
+        <v>0.99274825203969319</v>
       </c>
       <c r="BD26">
-        <v>145.63779129938152</v>
+        <v>132.94871260562454</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9301,16 +9301,16 @@
         <v>293</v>
       </c>
       <c r="Y27" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="Z27" t="s">
         <v>331</v>
       </c>
       <c r="AA27">
-        <v>0.99785055087302266</v>
+        <v>0.99694914525426248</v>
       </c>
       <c r="AB27">
-        <v>39.406567327917379</v>
+        <v>55.93233700518811</v>
       </c>
       <c r="AD27" t="s">
         <v>258</v>
@@ -9343,10 +9343,10 @@
         <v>423</v>
       </c>
       <c r="AO27">
-        <v>0.99819477422379621</v>
+        <v>0.99870468347604002</v>
       </c>
       <c r="AP27">
-        <v>33.095805897069312</v>
+        <v>23.747469605933066</v>
       </c>
       <c r="AR27" t="s">
         <v>258</v>
@@ -9379,10 +9379,10 @@
         <v>509</v>
       </c>
       <c r="BC27">
-        <v>0.99331560634963856</v>
+        <v>0.99631611357458616</v>
       </c>
       <c r="BD27">
-        <v>122.54721692329359</v>
+        <v>67.537917799253435</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9447,16 +9447,16 @@
         <v>295</v>
       </c>
       <c r="Y28" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="Z28" t="s">
         <v>332</v>
       </c>
       <c r="AA28">
-        <v>0.99844993371564827</v>
+        <v>0.99783229073864799</v>
       </c>
       <c r="AB28">
-        <v>28.417881879781795</v>
+        <v>39.741336458120216</v>
       </c>
       <c r="AD28" t="s">
         <v>258</v>
@@ -9489,10 +9489,10 @@
         <v>425</v>
       </c>
       <c r="AO28">
-        <v>0.99766227319444256</v>
+        <v>0.99882525100456254</v>
       </c>
       <c r="AP28">
-        <v>42.858324768553842</v>
+        <v>21.53706491635322</v>
       </c>
       <c r="AR28" t="s">
         <v>258</v>
@@ -9525,10 +9525,10 @@
         <v>511</v>
       </c>
       <c r="BC28">
-        <v>0.99274825203969319</v>
+        <v>0.99647965026436902</v>
       </c>
       <c r="BD28">
-        <v>132.94871260562454</v>
+        <v>64.539745153233895</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9593,16 +9593,16 @@
         <v>297</v>
       </c>
       <c r="Y29" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="Z29" t="s">
         <v>333</v>
       </c>
       <c r="AA29">
-        <v>0.99844308301553419</v>
+        <v>0.99854419231621216</v>
       </c>
       <c r="AB29">
-        <v>28.543478048539875</v>
+        <v>26.689807536110646</v>
       </c>
       <c r="AD29" t="s">
         <v>258</v>
@@ -9635,10 +9635,10 @@
         <v>427</v>
       </c>
       <c r="AO29">
-        <v>0.99916669398891145</v>
+        <v>0.9997500752992049</v>
       </c>
       <c r="AP29">
-        <v>15.27727686995606</v>
+        <v>4.5819528479096752</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9745,10 +9745,10 @@
         <v>429</v>
       </c>
       <c r="AO30">
-        <v>0.99882525100456254</v>
+        <v>0.99625266957809566</v>
       </c>
       <c r="AP30">
-        <v>21.53706491635322</v>
+        <v>68.701057734912879</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9855,10 +9855,10 @@
         <v>431</v>
       </c>
       <c r="AO31">
-        <v>0.9997500752992049</v>
+        <v>0.99949680967458154</v>
       </c>
       <c r="AP31">
-        <v>4.5819528479096752</v>
+        <v>9.2251559660040208</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9965,10 +9965,10 @@
         <v>433</v>
       </c>
       <c r="AO32">
-        <v>0.99625266957809566</v>
+        <v>0.99811627933819014</v>
       </c>
       <c r="AP32">
-        <v>68.701057734912879</v>
+        <v>34.534878799847206</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10075,10 +10075,10 @@
         <v>435</v>
       </c>
       <c r="AO33">
-        <v>0.99738967567885828</v>
+        <v>0.99868644475480806</v>
       </c>
       <c r="AP33">
-        <v>47.855945887599148</v>
+        <v>24.081846161853086</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10185,10 +10185,10 @@
         <v>437</v>
       </c>
       <c r="AO34">
-        <v>0.99928399407691448</v>
+        <v>0.99787586239643478</v>
       </c>
       <c r="AP34">
-        <v>13.126775256568077</v>
+        <v>38.942522732029175</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -10381,7 +10381,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C61F55-7A34-4E96-8760-07CC70AD80BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0010C7AF-8015-4000-9FFC-BDB78B0C7CA9}">
   <dimension ref="B9:Z35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10493,7 +10493,7 @@
         <v>512</v>
       </c>
       <c r="K11" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="L11">
         <v>2.0485665253142935</v>
@@ -10526,7 +10526,7 @@
         <v>562</v>
       </c>
       <c r="X11" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="Y11">
         <v>7.5397499999999997</v>
@@ -10561,7 +10561,7 @@
         <v>514</v>
       </c>
       <c r="K12" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
       <c r="L12">
         <v>0.27827335220936616</v>
@@ -10594,7 +10594,7 @@
         <v>564</v>
       </c>
       <c r="X12" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="Y12">
         <v>23.645250000000001</v>
@@ -10629,7 +10629,7 @@
         <v>516</v>
       </c>
       <c r="K13" t="s">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="L13">
         <v>6.0169436033943411</v>
@@ -10662,7 +10662,7 @@
         <v>566</v>
       </c>
       <c r="X13" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="Y13">
         <v>36.9495</v>
@@ -10697,7 +10697,7 @@
         <v>518</v>
       </c>
       <c r="K14" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="L14">
         <v>1.974607487182084</v>
@@ -10730,7 +10730,7 @@
         <v>568</v>
       </c>
       <c r="X14" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="Y14">
         <v>35.276249999999997</v>
@@ -10765,7 +10765,7 @@
         <v>520</v>
       </c>
       <c r="K15" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="L15">
         <v>3.8785592894875776</v>
@@ -10798,7 +10798,7 @@
         <v>570</v>
       </c>
       <c r="X15" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="Y15">
         <v>20.849250000000001</v>
@@ -10833,7 +10833,7 @@
         <v>522</v>
       </c>
       <c r="K16" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="L16">
         <v>0.82556800193341606</v>
@@ -10866,7 +10866,7 @@
         <v>572</v>
       </c>
       <c r="X16" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="Y16">
         <v>2.3107500000000001</v>
@@ -10901,7 +10901,7 @@
         <v>524</v>
       </c>
       <c r="K17" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="L17">
         <v>1.3596128536185663</v>
@@ -10934,7 +10934,7 @@
         <v>574</v>
       </c>
       <c r="X17" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="Y17">
         <v>9.8947500000000002</v>
@@ -10969,7 +10969,7 @@
         <v>526</v>
       </c>
       <c r="K18" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="L18">
         <v>0.4055180903599177</v>
@@ -11002,7 +11002,7 @@
         <v>576</v>
       </c>
       <c r="X18" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="Y18">
         <v>8.6842500000000005</v>
@@ -11037,7 +11037,7 @@
         <v>528</v>
       </c>
       <c r="K19" t="s">
-        <v>395</v>
+        <v>436</v>
       </c>
       <c r="L19">
         <v>1.0707529779056921</v>
@@ -11070,7 +11070,7 @@
         <v>578</v>
       </c>
       <c r="X19" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="Y19">
         <v>29.875499999999999</v>
@@ -11105,7 +11105,7 @@
         <v>530</v>
       </c>
       <c r="K20" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="L20">
         <v>0.55837077614555952</v>
@@ -11138,7 +11138,7 @@
         <v>580</v>
       </c>
       <c r="X20" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="Y20">
         <v>40.528500000000001</v>
@@ -11173,7 +11173,7 @@
         <v>532</v>
       </c>
       <c r="K21" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="L21">
         <v>1.1191802126669304</v>
@@ -11206,7 +11206,7 @@
         <v>582</v>
       </c>
       <c r="X21" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="Y21">
         <v>3.69225</v>
@@ -11241,7 +11241,7 @@
         <v>534</v>
       </c>
       <c r="K22" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="L22">
         <v>3.9321545280460359</v>
@@ -11274,7 +11274,7 @@
         <v>584</v>
       </c>
       <c r="X22" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="Y22">
         <v>42.84075</v>
@@ -11309,7 +11309,7 @@
         <v>536</v>
       </c>
       <c r="K23" t="s">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="L23">
         <v>1.2747581879814029</v>
@@ -11342,7 +11342,7 @@
         <v>586</v>
       </c>
       <c r="X23" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="Y23">
         <v>21.626249999999999</v>
@@ -11377,7 +11377,7 @@
         <v>538</v>
       </c>
       <c r="K24" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="L24">
         <v>1.3895551399416923</v>
@@ -11410,7 +11410,7 @@
         <v>588</v>
       </c>
       <c r="X24" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="Y24">
         <v>29.77075</v>
@@ -11478,7 +11478,7 @@
         <v>590</v>
       </c>
       <c r="X25" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="Y25">
         <v>34.175249999999998</v>
@@ -11513,7 +11513,7 @@
         <v>542</v>
       </c>
       <c r="K26" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="L26">
         <v>2.2119542216758865</v>
@@ -11546,7 +11546,7 @@
         <v>592</v>
       </c>
       <c r="X26" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="Y26">
         <v>12.687749999999999</v>
@@ -11581,7 +11581,7 @@
         <v>544</v>
       </c>
       <c r="K27" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="L27">
         <v>7.9247611034863779</v>
@@ -11614,7 +11614,7 @@
         <v>594</v>
       </c>
       <c r="X27" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="Y27">
         <v>12.513</v>
@@ -11649,7 +11649,7 @@
         <v>546</v>
       </c>
       <c r="K28" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="L28">
         <v>4.3955340400007898</v>
@@ -11682,7 +11682,7 @@
         <v>596</v>
       </c>
       <c r="X28" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="Y28">
         <v>38.378999999999998</v>
@@ -11717,7 +11717,7 @@
         <v>548</v>
       </c>
       <c r="K29" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="L29">
         <v>0.5780310412144154</v>
@@ -11752,7 +11752,7 @@
         <v>550</v>
       </c>
       <c r="K30" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="L30">
         <v>0.33899815049521981</v>
@@ -11787,7 +11787,7 @@
         <v>552</v>
       </c>
       <c r="K31" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L31">
         <v>1.0010891133233775</v>
@@ -11822,7 +11822,7 @@
         <v>554</v>
       </c>
       <c r="K32" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="L32">
         <v>0.1594390600826095</v>
@@ -11857,7 +11857,7 @@
         <v>556</v>
       </c>
       <c r="K33" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="L33">
         <v>0.5482230079548871</v>
@@ -11892,7 +11892,7 @@
         <v>558</v>
       </c>
       <c r="K34" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="L34">
         <v>1.4643486628297562</v>
@@ -11927,7 +11927,7 @@
         <v>560</v>
       </c>
       <c r="K35" t="s">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="L35">
         <v>1.2331970370370371</v>
@@ -11942,7 +11942,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50588422-73D5-41BF-BA8E-0DF989573B7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9C260F-1D32-4F9A-AA59-4D5E770E5B62}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
